--- a/PCB Lattice/V1/BOM PPU_LITE_LATT_V1.xlsx
+++ b/PCB Lattice/V1/BOM PPU_LITE_LATT_V1.xlsx
@@ -4753,7 +4753,7 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>81</v>
